--- a/final_data_pipeline/output/325193longform_elec_options_nowhp.xlsx
+++ b/final_data_pipeline/output/325193longform_elec_options_nowhp.xlsx
@@ -1156,7 +1156,7 @@
         <v>198</v>
       </c>
       <c r="I4">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="J4">
         <v>8000</v>
@@ -1171,10 +1171,10 @@
         <v>2258215.741464195</v>
       </c>
       <c r="N4">
-        <v>1.667307692307692</v>
+        <v>1.816489556614144</v>
       </c>
       <c r="O4">
-        <v>1.799766355140187</v>
+        <v>1.977334632662277</v>
       </c>
       <c r="P4">
         <v>282.2769676830244</v>
@@ -1209,7 +1209,7 @@
         <v>198</v>
       </c>
       <c r="I5">
-        <v>10</v>
+        <v>20.68981481481483</v>
       </c>
       <c r="J5">
         <v>8000</v>
@@ -1224,10 +1224,10 @@
         <v>1385403.985728944</v>
       </c>
       <c r="N5">
-        <v>1.667307692307692</v>
+        <v>1.834960588773244</v>
       </c>
       <c r="O5">
-        <v>1.799766355140187</v>
+        <v>1.999528914098928</v>
       </c>
       <c r="P5">
         <v>173.175498216118</v>
@@ -1315,7 +1315,7 @@
         <v>198</v>
       </c>
       <c r="I7">
-        <v>10</v>
+        <v>13.76976495726495</v>
       </c>
       <c r="J7">
         <v>8000</v>
@@ -1330,10 +1330,10 @@
         <v>1893952.12230182</v>
       </c>
       <c r="N7">
-        <v>1.667307692307692</v>
+        <v>1.722817230984068</v>
       </c>
       <c r="O7">
-        <v>1.799766355140187</v>
+        <v>1.865490279279885</v>
       </c>
       <c r="P7">
         <v>236.7440152877275</v>
@@ -1368,7 +1368,7 @@
         <v>198</v>
       </c>
       <c r="I8">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="J8">
         <v>8000</v>
@@ -1383,10 +1383,10 @@
         <v>4064316.900281468</v>
       </c>
       <c r="N8">
-        <v>1.667307692307692</v>
+        <v>1.710268888048116</v>
       </c>
       <c r="O8">
-        <v>1.799766355140187</v>
+        <v>1.850597034134623</v>
       </c>
       <c r="P8">
         <v>508.0396125351835</v>
@@ -1474,7 +1474,7 @@
         <v>198</v>
       </c>
       <c r="I10">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="J10">
         <v>8000</v>
@@ -1489,10 +1489,10 @@
         <v>2780632.783891404</v>
       </c>
       <c r="N10">
-        <v>1.667307692307692</v>
+        <v>1.741255230125523</v>
       </c>
       <c r="O10">
-        <v>1.799766355140187</v>
+        <v>1.887411944869831</v>
       </c>
       <c r="P10">
         <v>347.5790979864255</v>
@@ -1580,7 +1580,7 @@
         <v>198</v>
       </c>
       <c r="I12">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="J12">
         <v>8000</v>
@@ -1595,10 +1595,10 @@
         <v>1107215.802854492</v>
       </c>
       <c r="N12">
-        <v>1.667307692307692</v>
+        <v>1.741255230125523</v>
       </c>
       <c r="O12">
-        <v>1.799766355140187</v>
+        <v>1.887411944869831</v>
       </c>
       <c r="P12">
         <v>138.4019753568115</v>
@@ -1739,7 +1739,7 @@
         <v>198</v>
       </c>
       <c r="I15">
-        <v>10</v>
+        <v>0.2777777777777778</v>
       </c>
       <c r="J15">
         <v>8000</v>
@@ -1754,10 +1754,10 @@
         <v>1103773.922375246</v>
       </c>
       <c r="N15">
-        <v>1.667307692307692</v>
+        <v>1.539390618149934</v>
       </c>
       <c r="O15">
-        <v>1.799766355140187</v>
+        <v>1.649857210851975</v>
       </c>
       <c r="P15">
         <v>137.9717402969058</v>
@@ -1792,7 +1792,7 @@
         <v>198</v>
       </c>
       <c r="I16">
-        <v>10</v>
+        <v>23.1435185185185</v>
       </c>
       <c r="J16">
         <v>8000</v>
@@ -1807,10 +1807,10 @@
         <v>1027975.411610765</v>
       </c>
       <c r="N16">
-        <v>1.667307692307692</v>
+        <v>1.878313199304596</v>
       </c>
       <c r="O16">
-        <v>1.799766355140187</v>
+        <v>2.051802890544073</v>
       </c>
       <c r="P16">
         <v>128.4969264513457</v>
@@ -1845,7 +1845,7 @@
         <v>199</v>
       </c>
       <c r="I17">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="J17">
         <v>8000</v>
@@ -1889,7 +1889,7 @@
         <v>198</v>
       </c>
       <c r="I18">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="J18">
         <v>8000</v>
@@ -1904,10 +1904,10 @@
         <v>2190178.576471585</v>
       </c>
       <c r="N18">
-        <v>1.667307692307692</v>
+        <v>1.733649767723692</v>
       </c>
       <c r="O18">
-        <v>1.799766355140187</v>
+        <v>1.878363999113278</v>
       </c>
       <c r="P18">
         <v>273.7723220589481</v>
@@ -1942,7 +1942,7 @@
         <v>198</v>
       </c>
       <c r="I19">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="J19">
         <v>8000</v>
@@ -1957,10 +1957,10 @@
         <v>3041581.489047246</v>
       </c>
       <c r="N19">
-        <v>1.667307692307692</v>
+        <v>1.60506628066433</v>
       </c>
       <c r="O19">
-        <v>1.799766355140187</v>
+        <v>1.726556533289058</v>
       </c>
       <c r="P19">
         <v>380.1976861309057</v>
@@ -2207,7 +2207,7 @@
         <v>198</v>
       </c>
       <c r="I24">
-        <v>10</v>
+        <v>13.46442495126706</v>
       </c>
       <c r="J24">
         <v>8000</v>
@@ -2222,10 +2222,10 @@
         <v>1678287.501873749</v>
       </c>
       <c r="N24">
-        <v>1.667307692307692</v>
+        <v>1.718183925313875</v>
       </c>
       <c r="O24">
-        <v>1.799766355140187</v>
+        <v>1.859988703490151</v>
       </c>
       <c r="P24">
         <v>209.7859377342186</v>
@@ -2260,7 +2260,7 @@
         <v>198</v>
       </c>
       <c r="I25">
-        <v>10</v>
+        <v>12.66820987654322</v>
       </c>
       <c r="J25">
         <v>8000</v>
@@ -2275,10 +2275,10 @@
         <v>820105.9974206667</v>
       </c>
       <c r="N25">
-        <v>1.667307692307692</v>
+        <v>1.706218364895326</v>
       </c>
       <c r="O25">
-        <v>1.799766355140187</v>
+        <v>1.845794074578076</v>
       </c>
       <c r="P25">
         <v>102.5132496775833</v>
@@ -2313,7 +2313,7 @@
         <v>198</v>
       </c>
       <c r="I26">
-        <v>10</v>
+        <v>0.2777777777777778</v>
       </c>
       <c r="J26">
         <v>8000</v>
@@ -2328,10 +2328,10 @@
         <v>1646468.666748252</v>
       </c>
       <c r="N26">
-        <v>1.667307692307692</v>
+        <v>1.539390618149934</v>
       </c>
       <c r="O26">
-        <v>1.799766355140187</v>
+        <v>1.649857210851975</v>
       </c>
       <c r="P26">
         <v>205.8085833435314</v>
@@ -2366,7 +2366,7 @@
         <v>198</v>
       </c>
       <c r="I27">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="J27">
         <v>8000</v>
@@ -2381,10 +2381,10 @@
         <v>1312553.069312523</v>
       </c>
       <c r="N27">
-        <v>1.667307692307692</v>
+        <v>1.733649767723692</v>
       </c>
       <c r="O27">
-        <v>1.799766355140187</v>
+        <v>1.878363999113278</v>
       </c>
       <c r="P27">
         <v>164.0691336640654</v>
@@ -2525,7 +2525,7 @@
         <v>198</v>
       </c>
       <c r="I30">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="J30">
         <v>8000</v>
@@ -2540,10 +2540,10 @@
         <v>595852.5374651274</v>
       </c>
       <c r="N30">
-        <v>1.667307692307692</v>
+        <v>1.741255230125523</v>
       </c>
       <c r="O30">
-        <v>1.799766355140187</v>
+        <v>1.887411944869831</v>
       </c>
       <c r="P30">
         <v>74.48156718314092</v>
@@ -2578,7 +2578,7 @@
         <v>198</v>
       </c>
       <c r="I31">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="J31">
         <v>8000</v>
@@ -2593,10 +2593,10 @@
         <v>810142.6164230106</v>
       </c>
       <c r="N31">
-        <v>1.667307692307692</v>
+        <v>1.816489556614144</v>
       </c>
       <c r="O31">
-        <v>1.799766355140187</v>
+        <v>1.977334632662277</v>
       </c>
       <c r="P31">
         <v>101.2678270528763</v>
@@ -2631,7 +2631,7 @@
         <v>198</v>
       </c>
       <c r="I32">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="J32">
         <v>8000</v>
@@ -2646,10 +2646,10 @@
         <v>2777627.954701636</v>
       </c>
       <c r="N32">
-        <v>1.667307692307692</v>
+        <v>1.558003327787022</v>
       </c>
       <c r="O32">
-        <v>1.799766355140187</v>
+        <v>1.671537070524412</v>
       </c>
       <c r="P32">
         <v>347.2034943377045</v>
@@ -2684,7 +2684,7 @@
         <v>198</v>
       </c>
       <c r="I33">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="J33">
         <v>8000</v>
@@ -2699,10 +2699,10 @@
         <v>2947409.087913847</v>
       </c>
       <c r="N33">
-        <v>1.667307692307692</v>
+        <v>1.733649767723692</v>
       </c>
       <c r="O33">
-        <v>1.799766355140187</v>
+        <v>1.878363999113278</v>
       </c>
       <c r="P33">
         <v>368.4261359892308</v>
@@ -2737,7 +2737,7 @@
         <v>198</v>
       </c>
       <c r="I34">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="J34">
         <v>8000</v>
@@ -2752,10 +2752,10 @@
         <v>2483437.855952705</v>
       </c>
       <c r="N34">
-        <v>1.667307692307692</v>
+        <v>1.60506628066433</v>
       </c>
       <c r="O34">
-        <v>1.799766355140187</v>
+        <v>1.726556533289058</v>
       </c>
       <c r="P34">
         <v>310.4297319940882</v>
@@ -2790,7 +2790,7 @@
         <v>198</v>
       </c>
       <c r="I35">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="J35">
         <v>8000</v>
@@ -2805,10 +2805,10 @@
         <v>2856512.628378315</v>
       </c>
       <c r="N35">
-        <v>1.667307692307692</v>
+        <v>1.60506628066433</v>
       </c>
       <c r="O35">
-        <v>1.799766355140187</v>
+        <v>1.726556533289058</v>
       </c>
       <c r="P35">
         <v>357.0640785472894</v>
@@ -2843,7 +2843,7 @@
         <v>198</v>
       </c>
       <c r="I36">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="J36">
         <v>8000</v>
@@ -2858,10 +2858,10 @@
         <v>2556924.380348116</v>
       </c>
       <c r="N36">
-        <v>1.667307692307692</v>
+        <v>1.60506628066433</v>
       </c>
       <c r="O36">
-        <v>1.799766355140187</v>
+        <v>1.726556533289058</v>
       </c>
       <c r="P36">
         <v>319.6155475435145</v>
@@ -2949,7 +2949,7 @@
         <v>198</v>
       </c>
       <c r="I38">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="J38">
         <v>8000</v>
@@ -2964,10 +2964,10 @@
         <v>2278261.491683062</v>
       </c>
       <c r="N38">
-        <v>1.667307692307692</v>
+        <v>1.733649767723692</v>
       </c>
       <c r="O38">
-        <v>1.799766355140187</v>
+        <v>1.878363999113278</v>
       </c>
       <c r="P38">
         <v>284.7826864603828</v>
@@ -3055,7 +3055,7 @@
         <v>198</v>
       </c>
       <c r="I40">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="J40">
         <v>8000</v>
@@ -3070,10 +3070,10 @@
         <v>2903601.841305105</v>
       </c>
       <c r="N40">
-        <v>1.667307692307692</v>
+        <v>1.733649767723692</v>
       </c>
       <c r="O40">
-        <v>1.799766355140187</v>
+        <v>1.878363999113278</v>
       </c>
       <c r="P40">
         <v>362.9502301631381</v>
@@ -3161,7 +3161,7 @@
         <v>198</v>
       </c>
       <c r="I42">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="J42">
         <v>8000</v>
@@ -3176,10 +3176,10 @@
         <v>1318086.774797843</v>
       </c>
       <c r="N42">
-        <v>1.667307692307692</v>
+        <v>1.733649767723692</v>
       </c>
       <c r="O42">
-        <v>1.799766355140187</v>
+        <v>1.878363999113278</v>
       </c>
       <c r="P42">
         <v>164.7608468497303</v>
@@ -3214,7 +3214,7 @@
         <v>198</v>
       </c>
       <c r="I43">
-        <v>10</v>
+        <v>13.76976495726495</v>
       </c>
       <c r="J43">
         <v>8000</v>
@@ -3229,10 +3229,10 @@
         <v>2510354.79953685</v>
       </c>
       <c r="N43">
-        <v>1.667307692307692</v>
+        <v>1.722817230984068</v>
       </c>
       <c r="O43">
-        <v>1.799766355140187</v>
+        <v>1.865490279279885</v>
       </c>
       <c r="P43">
         <v>313.7943499421062</v>
@@ -3267,7 +3267,7 @@
         <v>198</v>
       </c>
       <c r="I44">
-        <v>10</v>
+        <v>23.1435185185185</v>
       </c>
       <c r="J44">
         <v>8000</v>
@@ -3282,10 +3282,10 @@
         <v>669486.4867409088</v>
       </c>
       <c r="N44">
-        <v>1.667307692307692</v>
+        <v>1.878313199304596</v>
       </c>
       <c r="O44">
-        <v>1.799766355140187</v>
+        <v>2.051802890544073</v>
       </c>
       <c r="P44">
         <v>83.68581084261359</v>
@@ -3479,7 +3479,7 @@
         <v>198</v>
       </c>
       <c r="I48">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="J48">
         <v>8000</v>
@@ -3494,10 +3494,10 @@
         <v>2920541.848271188</v>
       </c>
       <c r="N48">
-        <v>1.667307692307692</v>
+        <v>1.60506628066433</v>
       </c>
       <c r="O48">
-        <v>1.799766355140187</v>
+        <v>1.726556533289058</v>
       </c>
       <c r="P48">
         <v>365.0677310338985</v>
@@ -3691,7 +3691,7 @@
         <v>198</v>
       </c>
       <c r="I52">
-        <v>10</v>
+        <v>13.76976495726495</v>
       </c>
       <c r="J52">
         <v>8000</v>
@@ -3706,10 +3706,10 @@
         <v>2012566.813205434</v>
       </c>
       <c r="N52">
-        <v>1.667307692307692</v>
+        <v>1.722817230984068</v>
       </c>
       <c r="O52">
-        <v>1.799766355140187</v>
+        <v>1.865490279279885</v>
       </c>
       <c r="P52">
         <v>251.5708516506792</v>
@@ -3744,7 +3744,7 @@
         <v>198</v>
       </c>
       <c r="I53">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="J53">
         <v>8000</v>
@@ -3759,10 +3759,10 @@
         <v>1346880.418718053</v>
       </c>
       <c r="N53">
-        <v>1.667307692307692</v>
+        <v>1.710268888048116</v>
       </c>
       <c r="O53">
-        <v>1.799766355140187</v>
+        <v>1.850597034134623</v>
       </c>
       <c r="P53">
         <v>168.3600523397566</v>
@@ -3797,7 +3797,7 @@
         <v>198</v>
       </c>
       <c r="I54">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="J54">
         <v>8000</v>
@@ -3812,10 +3812,10 @@
         <v>1684960.603978198</v>
       </c>
       <c r="N54">
-        <v>1.667307692307692</v>
+        <v>1.60506628066433</v>
       </c>
       <c r="O54">
-        <v>1.799766355140187</v>
+        <v>1.726556533289058</v>
       </c>
       <c r="P54">
         <v>210.6200754972747</v>
@@ -3850,7 +3850,7 @@
         <v>198</v>
       </c>
       <c r="I55">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="J55">
         <v>8000</v>
@@ -3865,10 +3865,10 @@
         <v>2141860.320628078</v>
       </c>
       <c r="N55">
-        <v>1.667307692307692</v>
+        <v>1.60506628066433</v>
       </c>
       <c r="O55">
-        <v>1.799766355140187</v>
+        <v>1.726556533289058</v>
       </c>
       <c r="P55">
         <v>267.7325400785097</v>
@@ -4009,7 +4009,7 @@
         <v>198</v>
       </c>
       <c r="I58">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="J58">
         <v>8000</v>
@@ -4024,10 +4024,10 @@
         <v>1524725.639891178</v>
       </c>
       <c r="N58">
-        <v>1.667307692307692</v>
+        <v>1.733649767723692</v>
       </c>
       <c r="O58">
-        <v>1.799766355140187</v>
+        <v>1.878363999113278</v>
       </c>
       <c r="P58">
         <v>190.5907049863973</v>
@@ -4115,7 +4115,7 @@
         <v>198</v>
       </c>
       <c r="I60">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="J60">
         <v>8000</v>
@@ -4130,10 +4130,10 @@
         <v>2720552.768076514</v>
       </c>
       <c r="N60">
-        <v>1.667307692307692</v>
+        <v>1.60506628066433</v>
       </c>
       <c r="O60">
-        <v>1.799766355140187</v>
+        <v>1.726556533289058</v>
       </c>
       <c r="P60">
         <v>340.0690960095643</v>
@@ -4221,7 +4221,7 @@
         <v>198</v>
       </c>
       <c r="I62">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="J62">
         <v>8000</v>
@@ -4236,10 +4236,10 @@
         <v>2466202.637697804</v>
       </c>
       <c r="N62">
-        <v>1.667307692307692</v>
+        <v>1.60506628066433</v>
       </c>
       <c r="O62">
-        <v>1.799766355140187</v>
+        <v>1.726556533289058</v>
       </c>
       <c r="P62">
         <v>308.2753297122255</v>
@@ -4274,7 +4274,7 @@
         <v>198</v>
       </c>
       <c r="I63">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="J63">
         <v>8000</v>
@@ -4289,10 +4289,10 @@
         <v>3005809.712978566</v>
       </c>
       <c r="N63">
-        <v>1.667307692307692</v>
+        <v>1.741255230125523</v>
       </c>
       <c r="O63">
-        <v>1.799766355140187</v>
+        <v>1.887411944869831</v>
       </c>
       <c r="P63">
         <v>375.7262141223207</v>
@@ -4327,7 +4327,7 @@
         <v>198</v>
       </c>
       <c r="I64">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="J64">
         <v>8000</v>
@@ -4342,10 +4342,10 @@
         <v>921084.8261774092</v>
       </c>
       <c r="N64">
-        <v>1.667307692307692</v>
+        <v>1.816489556614144</v>
       </c>
       <c r="O64">
-        <v>1.799766355140187</v>
+        <v>1.977334632662277</v>
       </c>
       <c r="P64">
         <v>115.1356032721762</v>
@@ -4380,7 +4380,7 @@
         <v>198</v>
       </c>
       <c r="I65">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="J65">
         <v>8000</v>
@@ -4395,10 +4395,10 @@
         <v>2622274.520140451</v>
       </c>
       <c r="N65">
-        <v>1.667307692307692</v>
+        <v>1.60506628066433</v>
       </c>
       <c r="O65">
-        <v>1.799766355140187</v>
+        <v>1.726556533289058</v>
       </c>
       <c r="P65">
         <v>327.7843150175564</v>
@@ -4486,7 +4486,7 @@
         <v>198</v>
       </c>
       <c r="I67">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="J67">
         <v>8000</v>
@@ -4501,10 +4501,10 @@
         <v>2954302.873979798</v>
       </c>
       <c r="N67">
-        <v>1.667307692307692</v>
+        <v>1.60506628066433</v>
       </c>
       <c r="O67">
-        <v>1.799766355140187</v>
+        <v>1.726556533289058</v>
       </c>
       <c r="P67">
         <v>369.2878592474747</v>
@@ -4698,7 +4698,7 @@
         <v>198</v>
       </c>
       <c r="I71">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="J71">
         <v>8000</v>
@@ -4713,10 +4713,10 @@
         <v>2908499.61871628</v>
       </c>
       <c r="N71">
-        <v>1.667307692307692</v>
+        <v>1.710268888048116</v>
       </c>
       <c r="O71">
-        <v>1.799766355140187</v>
+        <v>1.850597034134623</v>
       </c>
       <c r="P71">
         <v>363.562452339535</v>
@@ -4751,7 +4751,7 @@
         <v>198</v>
       </c>
       <c r="I72">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="J72">
         <v>8000</v>
@@ -4766,10 +4766,10 @@
         <v>1657274.098177803</v>
       </c>
       <c r="N72">
-        <v>1.667307692307692</v>
+        <v>1.60506628066433</v>
       </c>
       <c r="O72">
-        <v>1.799766355140187</v>
+        <v>1.726556533289058</v>
       </c>
       <c r="P72">
         <v>207.1592622722254</v>
@@ -4804,7 +4804,7 @@
         <v>198</v>
       </c>
       <c r="I73">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="J73">
         <v>8000</v>
@@ -4819,10 +4819,10 @@
         <v>1142515.885492662</v>
       </c>
       <c r="N73">
-        <v>1.667307692307692</v>
+        <v>1.60506628066433</v>
       </c>
       <c r="O73">
-        <v>1.799766355140187</v>
+        <v>1.726556533289058</v>
       </c>
       <c r="P73">
         <v>142.8144856865828</v>
@@ -4857,7 +4857,7 @@
         <v>198</v>
       </c>
       <c r="I74">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="J74">
         <v>8000</v>
@@ -4872,10 +4872,10 @@
         <v>1523808.376243776</v>
       </c>
       <c r="N74">
-        <v>1.667307692307692</v>
+        <v>1.60506628066433</v>
       </c>
       <c r="O74">
-        <v>1.799766355140187</v>
+        <v>1.726556533289058</v>
       </c>
       <c r="P74">
         <v>190.476047030472</v>
@@ -4910,7 +4910,7 @@
         <v>198</v>
       </c>
       <c r="I75">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="J75">
         <v>8000</v>
@@ -4925,10 +4925,10 @@
         <v>1292443.014829065</v>
       </c>
       <c r="N75">
-        <v>1.667307692307692</v>
+        <v>1.733649767723692</v>
       </c>
       <c r="O75">
-        <v>1.799766355140187</v>
+        <v>1.878363999113278</v>
       </c>
       <c r="P75">
         <v>161.5553768536331</v>
@@ -4963,7 +4963,7 @@
         <v>199</v>
       </c>
       <c r="I76">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="J76">
         <v>8000</v>
@@ -5010,7 +5010,7 @@
         <v>198</v>
       </c>
       <c r="I77">
-        <v>10</v>
+        <v>23.1435185185185</v>
       </c>
       <c r="J77">
         <v>8000</v>
@@ -5025,10 +5025,10 @@
         <v>991721.7135719409</v>
       </c>
       <c r="N77">
-        <v>1.667307692307692</v>
+        <v>1.878313199304596</v>
       </c>
       <c r="O77">
-        <v>1.799766355140187</v>
+        <v>2.051802890544073</v>
       </c>
       <c r="P77">
         <v>123.9652141964926</v>
@@ -5063,7 +5063,7 @@
         <v>199</v>
       </c>
       <c r="I78">
-        <v>10</v>
+        <v>23.1435185185185</v>
       </c>
       <c r="J78">
         <v>8000</v>
@@ -5110,7 +5110,7 @@
         <v>198</v>
       </c>
       <c r="I79">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="J79">
         <v>8000</v>
@@ -5125,10 +5125,10 @@
         <v>1593598.734808762</v>
       </c>
       <c r="N79">
-        <v>1.667307692307692</v>
+        <v>1.753361536861086</v>
       </c>
       <c r="O79">
-        <v>1.799766355140187</v>
+        <v>1.901830374152252</v>
       </c>
       <c r="P79">
         <v>199.1998418510953</v>
@@ -5216,7 +5216,7 @@
         <v>198</v>
       </c>
       <c r="I81">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="J81">
         <v>8000</v>
@@ -5231,10 +5231,10 @@
         <v>982276.4028655075</v>
       </c>
       <c r="N81">
-        <v>1.667307692307692</v>
+        <v>1.558003327787022</v>
       </c>
       <c r="O81">
-        <v>1.799766355140187</v>
+        <v>1.671537070524412</v>
       </c>
       <c r="P81">
         <v>122.7845503581885</v>
@@ -5375,7 +5375,7 @@
         <v>198</v>
       </c>
       <c r="I84">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="J84">
         <v>8000</v>
@@ -5390,10 +5390,10 @@
         <v>1314318.31232526</v>
       </c>
       <c r="N84">
-        <v>1.667307692307692</v>
+        <v>1.741255230125523</v>
       </c>
       <c r="O84">
-        <v>1.799766355140187</v>
+        <v>1.887411944869831</v>
       </c>
       <c r="P84">
         <v>164.2897890406575</v>
@@ -5481,7 +5481,7 @@
         <v>198</v>
       </c>
       <c r="I86">
-        <v>10</v>
+        <v>23.1435185185185</v>
       </c>
       <c r="J86">
         <v>8000</v>
@@ -5496,10 +5496,10 @@
         <v>3075146.711350008</v>
       </c>
       <c r="N86">
-        <v>1.667307692307692</v>
+        <v>1.878313199304596</v>
       </c>
       <c r="O86">
-        <v>1.799766355140187</v>
+        <v>2.051802890544073</v>
       </c>
       <c r="P86">
         <v>384.393338918751</v>
@@ -5587,7 +5587,7 @@
         <v>198</v>
       </c>
       <c r="I88">
-        <v>10</v>
+        <v>20.68981481481483</v>
       </c>
       <c r="J88">
         <v>8000</v>
@@ -5602,10 +5602,10 @@
         <v>1585626.523830593</v>
       </c>
       <c r="N88">
-        <v>1.667307692307692</v>
+        <v>1.834960588773244</v>
       </c>
       <c r="O88">
-        <v>1.799766355140187</v>
+        <v>1.999528914098928</v>
       </c>
       <c r="P88">
         <v>198.2033154788241</v>
@@ -5640,7 +5640,7 @@
         <v>198</v>
       </c>
       <c r="I89">
-        <v>10</v>
+        <v>21.28240740740739</v>
       </c>
       <c r="J89">
         <v>8000</v>
@@ -5655,10 +5655,10 @@
         <v>3091809.581187812</v>
       </c>
       <c r="N89">
-        <v>1.667307692307692</v>
+        <v>1.845246332384497</v>
       </c>
       <c r="O89">
-        <v>1.799766355140187</v>
+        <v>2.011908101571946</v>
       </c>
       <c r="P89">
         <v>386.4761976484764</v>
@@ -5693,7 +5693,7 @@
         <v>198</v>
       </c>
       <c r="I90">
-        <v>10</v>
+        <v>0.2777777777777778</v>
       </c>
       <c r="J90">
         <v>8000</v>
@@ -5708,10 +5708,10 @@
         <v>1016254.318500598</v>
       </c>
       <c r="N90">
-        <v>1.667307692307692</v>
+        <v>1.539390618149934</v>
       </c>
       <c r="O90">
-        <v>1.799766355140187</v>
+        <v>1.649857210851975</v>
       </c>
       <c r="P90">
         <v>127.0317898125748</v>
@@ -5852,7 +5852,7 @@
         <v>198</v>
       </c>
       <c r="I93">
-        <v>10</v>
+        <v>3.38888888888889</v>
       </c>
       <c r="J93">
         <v>8000</v>
@@ -5867,10 +5867,10 @@
         <v>977647.9115872314</v>
       </c>
       <c r="N93">
-        <v>1.667307692307692</v>
+        <v>1.578134831460674</v>
       </c>
       <c r="O93">
-        <v>1.799766355140187</v>
+        <v>1.695036674816626</v>
       </c>
       <c r="P93">
         <v>122.2059889484039</v>
@@ -5958,7 +5958,7 @@
         <v>198</v>
       </c>
       <c r="I95">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="J95">
         <v>8000</v>
@@ -5973,10 +5973,10 @@
         <v>2199769.930998127</v>
       </c>
       <c r="N95">
-        <v>1.667307692307692</v>
+        <v>1.710268888048116</v>
       </c>
       <c r="O95">
-        <v>1.799766355140187</v>
+        <v>1.850597034134623</v>
       </c>
       <c r="P95">
         <v>274.9712413747659</v>
@@ -6064,7 +6064,7 @@
         <v>198</v>
       </c>
       <c r="I97">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="J97">
         <v>8000</v>
@@ -6079,10 +6079,10 @@
         <v>1684037.315610615</v>
       </c>
       <c r="N97">
-        <v>1.667307692307692</v>
+        <v>1.733649767723692</v>
       </c>
       <c r="O97">
-        <v>1.799766355140187</v>
+        <v>1.878363999113278</v>
       </c>
       <c r="P97">
         <v>210.5046644513268</v>
@@ -6117,7 +6117,7 @@
         <v>198</v>
       </c>
       <c r="I98">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="J98">
         <v>8000</v>
@@ -6132,10 +6132,10 @@
         <v>1868357.604797184</v>
       </c>
       <c r="N98">
-        <v>1.667307692307692</v>
+        <v>1.60506628066433</v>
       </c>
       <c r="O98">
-        <v>1.799766355140187</v>
+        <v>1.726556533289058</v>
       </c>
       <c r="P98">
         <v>233.544700599648</v>
@@ -6223,7 +6223,7 @@
         <v>198</v>
       </c>
       <c r="I100">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="J100">
         <v>8000</v>
@@ -6238,10 +6238,10 @@
         <v>1504624.161010647</v>
       </c>
       <c r="N100">
-        <v>1.667307692307692</v>
+        <v>1.816489556614144</v>
       </c>
       <c r="O100">
-        <v>1.799766355140187</v>
+        <v>1.977334632662277</v>
       </c>
       <c r="P100">
         <v>188.0780201263309</v>
@@ -6276,7 +6276,7 @@
         <v>198</v>
       </c>
       <c r="I101">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="J101">
         <v>8000</v>
@@ -6291,10 +6291,10 @@
         <v>7608072.371951163</v>
       </c>
       <c r="N101">
-        <v>1.667307692307692</v>
+        <v>1.710268888048116</v>
       </c>
       <c r="O101">
-        <v>1.799766355140187</v>
+        <v>1.850597034134623</v>
       </c>
       <c r="P101">
         <v>951.0090464938953</v>
@@ -6329,7 +6329,7 @@
         <v>198</v>
       </c>
       <c r="I102">
-        <v>10</v>
+        <v>13.76976495726495</v>
       </c>
       <c r="J102">
         <v>8000</v>
@@ -6344,10 +6344,10 @@
         <v>449359.7793446233</v>
       </c>
       <c r="N102">
-        <v>1.667307692307692</v>
+        <v>1.722817230984068</v>
       </c>
       <c r="O102">
-        <v>1.799766355140187</v>
+        <v>1.865490279279885</v>
       </c>
       <c r="P102">
         <v>56.16997241807792</v>
@@ -6435,7 +6435,7 @@
         <v>198</v>
       </c>
       <c r="I104">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="J104">
         <v>8000</v>
@@ -6450,10 +6450,10 @@
         <v>728644.7203682611</v>
       </c>
       <c r="N104">
-        <v>1.667307692307692</v>
+        <v>1.816489556614144</v>
       </c>
       <c r="O104">
-        <v>1.799766355140187</v>
+        <v>1.977334632662277</v>
       </c>
       <c r="P104">
         <v>91.08059004603263</v>
@@ -6541,7 +6541,7 @@
         <v>198</v>
       </c>
       <c r="I106">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="J106">
         <v>8000</v>
@@ -6556,10 +6556,10 @@
         <v>1229195.040902202</v>
       </c>
       <c r="N106">
-        <v>1.667307692307692</v>
+        <v>1.741255230125523</v>
       </c>
       <c r="O106">
-        <v>1.799766355140187</v>
+        <v>1.887411944869831</v>
       </c>
       <c r="P106">
         <v>153.6493801127752</v>
@@ -6594,7 +6594,7 @@
         <v>198</v>
       </c>
       <c r="I107">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="J107">
         <v>8000</v>
@@ -6609,10 +6609,10 @@
         <v>2621522.936297998</v>
       </c>
       <c r="N107">
-        <v>1.667307692307692</v>
+        <v>1.60506628066433</v>
       </c>
       <c r="O107">
-        <v>1.799766355140187</v>
+        <v>1.726556533289058</v>
       </c>
       <c r="P107">
         <v>327.6903670372498</v>
@@ -6700,7 +6700,7 @@
         <v>198</v>
       </c>
       <c r="I109">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="J109">
         <v>8000</v>
@@ -6715,10 +6715,10 @@
         <v>1624318.279603451</v>
       </c>
       <c r="N109">
-        <v>1.667307692307692</v>
+        <v>1.733649767723692</v>
       </c>
       <c r="O109">
-        <v>1.799766355140187</v>
+        <v>1.878363999113278</v>
       </c>
       <c r="P109">
         <v>203.0397849504314</v>
@@ -6753,7 +6753,7 @@
         <v>198</v>
       </c>
       <c r="I110">
-        <v>10</v>
+        <v>13.76976495726495</v>
       </c>
       <c r="J110">
         <v>8000</v>
@@ -6768,10 +6768,10 @@
         <v>2715847.461615943</v>
       </c>
       <c r="N110">
-        <v>1.667307692307692</v>
+        <v>1.722817230984068</v>
       </c>
       <c r="O110">
-        <v>1.799766355140187</v>
+        <v>1.865490279279885</v>
       </c>
       <c r="P110">
         <v>339.4809327019929</v>
@@ -6806,7 +6806,7 @@
         <v>198</v>
       </c>
       <c r="I111">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="J111">
         <v>8000</v>
@@ -6821,10 +6821,10 @@
         <v>1268845.230586751</v>
       </c>
       <c r="N111">
-        <v>1.667307692307692</v>
+        <v>1.816489556614144</v>
       </c>
       <c r="O111">
-        <v>1.799766355140187</v>
+        <v>1.977334632662277</v>
       </c>
       <c r="P111">
         <v>158.6056538233439</v>
@@ -6965,7 +6965,7 @@
         <v>198</v>
       </c>
       <c r="I114">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="J114">
         <v>8000</v>
@@ -6980,10 +6980,10 @@
         <v>1066785.152830207</v>
       </c>
       <c r="N114">
-        <v>1.667307692307692</v>
+        <v>1.60506628066433</v>
       </c>
       <c r="O114">
-        <v>1.799766355140187</v>
+        <v>1.726556533289058</v>
       </c>
       <c r="P114">
         <v>133.3481441037758</v>
@@ -7071,7 +7071,7 @@
         <v>198</v>
       </c>
       <c r="I116">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="J116">
         <v>8000</v>
@@ -7086,10 +7086,10 @@
         <v>1541402.500865458</v>
       </c>
       <c r="N116">
-        <v>1.667307692307692</v>
+        <v>1.733649767723692</v>
       </c>
       <c r="O116">
-        <v>1.799766355140187</v>
+        <v>1.878363999113278</v>
       </c>
       <c r="P116">
         <v>192.6753126081823</v>
@@ -7230,7 +7230,7 @@
         <v>198</v>
       </c>
       <c r="I119">
-        <v>10</v>
+        <v>-0.763888888888889</v>
       </c>
       <c r="J119">
         <v>8000</v>
@@ -7245,10 +7245,10 @@
         <v>821716.1038887687</v>
       </c>
       <c r="N119">
-        <v>1.667307692307692</v>
+        <v>1.526839873899337</v>
       </c>
       <c r="O119">
-        <v>1.799766355140187</v>
+        <v>1.635263592404765</v>
       </c>
       <c r="P119">
         <v>102.7145129860961</v>
@@ -7336,7 +7336,7 @@
         <v>198</v>
       </c>
       <c r="I121">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="J121">
         <v>8000</v>
@@ -7351,10 +7351,10 @@
         <v>1198054.768471886</v>
       </c>
       <c r="N121">
-        <v>1.667307692307692</v>
+        <v>1.60506628066433</v>
       </c>
       <c r="O121">
-        <v>1.799766355140187</v>
+        <v>1.726556533289058</v>
       </c>
       <c r="P121">
         <v>149.7568460589858</v>
@@ -7442,7 +7442,7 @@
         <v>198</v>
       </c>
       <c r="I123">
-        <v>10</v>
+        <v>21.19907407407406</v>
       </c>
       <c r="J123">
         <v>8000</v>
@@ -7457,10 +7457,10 @@
         <v>1451154.769413249</v>
       </c>
       <c r="N123">
-        <v>1.667307692307692</v>
+        <v>1.843792937469916</v>
       </c>
       <c r="O123">
-        <v>1.799766355140187</v>
+        <v>2.010158024452713</v>
       </c>
       <c r="P123">
         <v>181.3943461766561</v>
@@ -7495,7 +7495,7 @@
         <v>198</v>
       </c>
       <c r="I124">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="J124">
         <v>8000</v>
@@ -7510,10 +7510,10 @@
         <v>3459969.688126595</v>
       </c>
       <c r="N124">
-        <v>1.667307692307692</v>
+        <v>1.60506628066433</v>
       </c>
       <c r="O124">
-        <v>1.799766355140187</v>
+        <v>1.726556533289058</v>
       </c>
       <c r="P124">
         <v>432.4962110158243</v>
@@ -7548,7 +7548,7 @@
         <v>198</v>
       </c>
       <c r="I125">
-        <v>10</v>
+        <v>13.46442495126706</v>
       </c>
       <c r="J125">
         <v>8000</v>
@@ -7563,10 +7563,10 @@
         <v>1574500.371838199</v>
       </c>
       <c r="N125">
-        <v>1.667307692307692</v>
+        <v>1.718183925313875</v>
       </c>
       <c r="O125">
-        <v>1.799766355140187</v>
+        <v>1.859988703490151</v>
       </c>
       <c r="P125">
         <v>196.8125464797749</v>
@@ -7601,7 +7601,7 @@
         <v>198</v>
       </c>
       <c r="I126">
-        <v>10</v>
+        <v>13.76976495726495</v>
       </c>
       <c r="J126">
         <v>8000</v>
@@ -7616,10 +7616,10 @@
         <v>3181282.700580821</v>
       </c>
       <c r="N126">
-        <v>1.667307692307692</v>
+        <v>1.722817230984068</v>
       </c>
       <c r="O126">
-        <v>1.799766355140187</v>
+        <v>1.865490279279885</v>
       </c>
       <c r="P126">
         <v>397.6603375726027</v>
@@ -7654,7 +7654,7 @@
         <v>198</v>
       </c>
       <c r="I127">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="J127">
         <v>8000</v>
@@ -7669,10 +7669,10 @@
         <v>2299444.407835902</v>
       </c>
       <c r="N127">
-        <v>1.667307692307692</v>
+        <v>1.819666609086197</v>
       </c>
       <c r="O127">
-        <v>1.799766355140187</v>
+        <v>1.981148790245761</v>
       </c>
       <c r="P127">
         <v>287.4305509794878</v>
@@ -7707,7 +7707,7 @@
         <v>198</v>
       </c>
       <c r="I128">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="J128">
         <v>8000</v>
@@ -7722,10 +7722,10 @@
         <v>2725828.355184955</v>
       </c>
       <c r="N128">
-        <v>1.667307692307692</v>
+        <v>1.558003327787022</v>
       </c>
       <c r="O128">
-        <v>1.799766355140187</v>
+        <v>1.671537070524412</v>
       </c>
       <c r="P128">
         <v>340.7285443981193</v>
@@ -7760,7 +7760,7 @@
         <v>198</v>
       </c>
       <c r="I129">
-        <v>10</v>
+        <v>13.76976495726495</v>
       </c>
       <c r="J129">
         <v>8000</v>
@@ -7775,10 +7775,10 @@
         <v>2674909.487992921</v>
       </c>
       <c r="N129">
-        <v>1.667307692307692</v>
+        <v>1.722817230984068</v>
       </c>
       <c r="O129">
-        <v>1.799766355140187</v>
+        <v>1.865490279279885</v>
       </c>
       <c r="P129">
         <v>334.3636859991152</v>
@@ -7813,7 +7813,7 @@
         <v>198</v>
       </c>
       <c r="I130">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="J130">
         <v>8000</v>
@@ -7828,10 +7828,10 @@
         <v>2403413.003981964</v>
       </c>
       <c r="N130">
-        <v>1.667307692307692</v>
+        <v>1.60506628066433</v>
       </c>
       <c r="O130">
-        <v>1.799766355140187</v>
+        <v>1.726556533289058</v>
       </c>
       <c r="P130">
         <v>300.4266254977455</v>
@@ -7866,7 +7866,7 @@
         <v>198</v>
       </c>
       <c r="I131">
-        <v>10</v>
+        <v>13.46442495126706</v>
       </c>
       <c r="J131">
         <v>8000</v>
@@ -7881,10 +7881,10 @@
         <v>809246.4392962373</v>
       </c>
       <c r="N131">
-        <v>1.667307692307692</v>
+        <v>1.718183925313875</v>
       </c>
       <c r="O131">
-        <v>1.799766355140187</v>
+        <v>1.859988703490151</v>
       </c>
       <c r="P131">
         <v>101.1558049120297</v>
@@ -8078,7 +8078,7 @@
         <v>198</v>
       </c>
       <c r="I135">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="J135">
         <v>8000</v>
@@ -8093,10 +8093,10 @@
         <v>2580155.701362152</v>
       </c>
       <c r="N135">
-        <v>1.667307692307692</v>
+        <v>1.558003327787022</v>
       </c>
       <c r="O135">
-        <v>1.799766355140187</v>
+        <v>1.671537070524412</v>
       </c>
       <c r="P135">
         <v>322.519462670269</v>
@@ -8131,7 +8131,7 @@
         <v>198</v>
       </c>
       <c r="I136">
-        <v>10</v>
+        <v>0.2777777777777778</v>
       </c>
       <c r="J136">
         <v>8000</v>
@@ -8146,10 +8146,10 @@
         <v>1033112.991744251</v>
       </c>
       <c r="N136">
-        <v>1.667307692307692</v>
+        <v>1.539390618149934</v>
       </c>
       <c r="O136">
-        <v>1.799766355140187</v>
+        <v>1.649857210851975</v>
       </c>
       <c r="P136">
         <v>129.1391239680313</v>
@@ -8184,7 +8184,7 @@
         <v>198</v>
       </c>
       <c r="I137">
-        <v>10</v>
+        <v>21.28240740740739</v>
       </c>
       <c r="J137">
         <v>8000</v>
@@ -8199,10 +8199,10 @@
         <v>1811631.851942502</v>
       </c>
       <c r="N137">
-        <v>1.667307692307692</v>
+        <v>1.845246332384497</v>
       </c>
       <c r="O137">
-        <v>1.799766355140187</v>
+        <v>2.011908101571946</v>
       </c>
       <c r="P137">
         <v>226.4539814928127</v>
@@ -8237,7 +8237,7 @@
         <v>198</v>
       </c>
       <c r="I138">
-        <v>10</v>
+        <v>13.46442495126706</v>
       </c>
       <c r="J138">
         <v>8000</v>
@@ -8252,10 +8252,10 @@
         <v>803034.9527906692</v>
       </c>
       <c r="N138">
-        <v>1.667307692307692</v>
+        <v>1.718183925313875</v>
       </c>
       <c r="O138">
-        <v>1.799766355140187</v>
+        <v>1.859988703490151</v>
       </c>
       <c r="P138">
         <v>100.3793690988336</v>
@@ -8290,7 +8290,7 @@
         <v>198</v>
       </c>
       <c r="I139">
-        <v>10</v>
+        <v>12.66820987654322</v>
       </c>
       <c r="J139">
         <v>8000</v>
@@ -8305,10 +8305,10 @@
         <v>614140.3948074443</v>
       </c>
       <c r="N139">
-        <v>1.667307692307692</v>
+        <v>1.706218364895326</v>
       </c>
       <c r="O139">
-        <v>1.799766355140187</v>
+        <v>1.845794074578076</v>
       </c>
       <c r="P139">
         <v>76.76754935093054</v>
@@ -8449,7 +8449,7 @@
         <v>198</v>
       </c>
       <c r="I142">
-        <v>10</v>
+        <v>21.19907407407406</v>
       </c>
       <c r="J142">
         <v>8000</v>
@@ -8464,10 +8464,10 @@
         <v>837774.995528528</v>
       </c>
       <c r="N142">
-        <v>1.667307692307692</v>
+        <v>1.843792937469916</v>
       </c>
       <c r="O142">
-        <v>1.799766355140187</v>
+        <v>2.010158024452713</v>
       </c>
       <c r="P142">
         <v>104.721874441066</v>
@@ -8555,7 +8555,7 @@
         <v>198</v>
       </c>
       <c r="I144">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="J144">
         <v>8000</v>
@@ -8570,10 +8570,10 @@
         <v>669147.5962307844</v>
       </c>
       <c r="N144">
-        <v>1.667307692307692</v>
+        <v>1.559675747705064</v>
       </c>
       <c r="O144">
-        <v>1.799766355140187</v>
+        <v>1.673487286771806</v>
       </c>
       <c r="P144">
         <v>83.64344952884805</v>
@@ -8661,7 +8661,7 @@
         <v>198</v>
       </c>
       <c r="I146">
-        <v>10</v>
+        <v>13.76976495726495</v>
       </c>
       <c r="J146">
         <v>8000</v>
@@ -8676,10 +8676,10 @@
         <v>1852672.245808584</v>
       </c>
       <c r="N146">
-        <v>1.667307692307692</v>
+        <v>1.722817230984068</v>
       </c>
       <c r="O146">
-        <v>1.799766355140187</v>
+        <v>1.865490279279885</v>
       </c>
       <c r="P146">
         <v>231.584030726073</v>
@@ -8714,7 +8714,7 @@
         <v>198</v>
       </c>
       <c r="I147">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="J147">
         <v>8000</v>
@@ -8729,10 +8729,10 @@
         <v>783078.0671944573</v>
       </c>
       <c r="N147">
-        <v>1.667307692307692</v>
+        <v>1.733649767723692</v>
       </c>
       <c r="O147">
-        <v>1.799766355140187</v>
+        <v>1.878363999113278</v>
       </c>
       <c r="P147">
         <v>97.88475839930716</v>
@@ -8767,7 +8767,7 @@
         <v>198</v>
       </c>
       <c r="I148">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="J148">
         <v>8000</v>
@@ -8782,10 +8782,10 @@
         <v>1097407.299325043</v>
       </c>
       <c r="N148">
-        <v>1.667307692307692</v>
+        <v>1.60506628066433</v>
       </c>
       <c r="O148">
-        <v>1.799766355140187</v>
+        <v>1.726556533289058</v>
       </c>
       <c r="P148">
         <v>137.1759124156304</v>
@@ -8820,7 +8820,7 @@
         <v>198</v>
       </c>
       <c r="I149">
-        <v>10</v>
+        <v>21.28240740740739</v>
       </c>
       <c r="J149">
         <v>8000</v>
@@ -8835,10 +8835,10 @@
         <v>1927590.564201428</v>
       </c>
       <c r="N149">
-        <v>1.667307692307692</v>
+        <v>1.845246332384497</v>
       </c>
       <c r="O149">
-        <v>1.799766355140187</v>
+        <v>2.011908101571946</v>
       </c>
       <c r="P149">
         <v>240.9488205251785</v>
@@ -8873,7 +8873,7 @@
         <v>198</v>
       </c>
       <c r="I150">
-        <v>10</v>
+        <v>17.25771604938272</v>
       </c>
       <c r="J150">
         <v>8000</v>
@@ -8888,10 +8888,10 @@
         <v>705794.4629056097</v>
       </c>
       <c r="N150">
-        <v>1.667307692307692</v>
+        <v>1.777573720698044</v>
       </c>
       <c r="O150">
-        <v>1.799766355140187</v>
+        <v>1.930725790230997</v>
       </c>
       <c r="P150">
         <v>88.2243078632012</v>
@@ -8926,7 +8926,7 @@
         <v>198</v>
       </c>
       <c r="I151">
-        <v>10</v>
+        <v>20.68981481481483</v>
       </c>
       <c r="J151">
         <v>8000</v>
@@ -8941,10 +8941,10 @@
         <v>1725189.166800026</v>
       </c>
       <c r="N151">
-        <v>1.667307692307692</v>
+        <v>1.834960588773244</v>
       </c>
       <c r="O151">
-        <v>1.799766355140187</v>
+        <v>1.999528914098928</v>
       </c>
       <c r="P151">
         <v>215.6486458500033</v>
@@ -9032,7 +9032,7 @@
         <v>198</v>
       </c>
       <c r="I153">
-        <v>10</v>
+        <v>17.25771604938272</v>
       </c>
       <c r="J153">
         <v>8000</v>
@@ -9047,10 +9047,10 @@
         <v>1228047.331707914</v>
       </c>
       <c r="N153">
-        <v>1.667307692307692</v>
+        <v>1.777573720698044</v>
       </c>
       <c r="O153">
-        <v>1.799766355140187</v>
+        <v>1.930725790230997</v>
       </c>
       <c r="P153">
         <v>153.5059164634893</v>
@@ -9191,7 +9191,7 @@
         <v>198</v>
       </c>
       <c r="I156">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="J156">
         <v>8000</v>
@@ -9206,10 +9206,10 @@
         <v>1424340.246072165</v>
       </c>
       <c r="N156">
-        <v>1.667307692307692</v>
+        <v>1.733649767723692</v>
       </c>
       <c r="O156">
-        <v>1.799766355140187</v>
+        <v>1.878363999113278</v>
       </c>
       <c r="P156">
         <v>178.0425307590206</v>
@@ -9350,7 +9350,7 @@
         <v>198</v>
       </c>
       <c r="I159">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="J159">
         <v>8000</v>
@@ -9365,10 +9365,10 @@
         <v>3522274.331867946</v>
       </c>
       <c r="N159">
-        <v>1.667307692307692</v>
+        <v>1.733649767723692</v>
       </c>
       <c r="O159">
-        <v>1.799766355140187</v>
+        <v>1.878363999113278</v>
       </c>
       <c r="P159">
         <v>440.2842914834933</v>
@@ -9456,7 +9456,7 @@
         <v>198</v>
       </c>
       <c r="I161">
-        <v>10</v>
+        <v>13.46442495126706</v>
       </c>
       <c r="J161">
         <v>8000</v>
@@ -9471,10 +9471,10 @@
         <v>984314.2644663887</v>
       </c>
       <c r="N161">
-        <v>1.667307692307692</v>
+        <v>1.718183925313875</v>
       </c>
       <c r="O161">
-        <v>1.799766355140187</v>
+        <v>1.859988703490151</v>
       </c>
       <c r="P161">
         <v>123.0392830582986</v>
@@ -9562,7 +9562,7 @@
         <v>198</v>
       </c>
       <c r="I163">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="J163">
         <v>8000</v>
@@ -9577,10 +9577,10 @@
         <v>2677171.770420507</v>
       </c>
       <c r="N163">
-        <v>1.667307692307692</v>
+        <v>1.60506628066433</v>
       </c>
       <c r="O163">
-        <v>1.799766355140187</v>
+        <v>1.726556533289058</v>
       </c>
       <c r="P163">
         <v>334.6464713025633</v>
@@ -9615,7 +9615,7 @@
         <v>198</v>
       </c>
       <c r="I164">
-        <v>10</v>
+        <v>23.1435185185185</v>
       </c>
       <c r="J164">
         <v>8000</v>
@@ -9630,10 +9630,10 @@
         <v>1530488.284743338</v>
       </c>
       <c r="N164">
-        <v>1.667307692307692</v>
+        <v>1.878313199304596</v>
       </c>
       <c r="O164">
-        <v>1.799766355140187</v>
+        <v>2.051802890544073</v>
       </c>
       <c r="P164">
         <v>191.3110355929172</v>
@@ -9668,7 +9668,7 @@
         <v>198</v>
       </c>
       <c r="I165">
-        <v>10</v>
+        <v>13.46442495126706</v>
       </c>
       <c r="J165">
         <v>8000</v>
@@ -9683,10 +9683,10 @@
         <v>287972.587523181</v>
       </c>
       <c r="N165">
-        <v>1.667307692307692</v>
+        <v>1.718183925313875</v>
       </c>
       <c r="O165">
-        <v>1.799766355140187</v>
+        <v>1.859988703490151</v>
       </c>
       <c r="P165">
         <v>35.99657344039763</v>
@@ -9721,7 +9721,7 @@
         <v>198</v>
       </c>
       <c r="I166">
-        <v>10</v>
+        <v>13.76976495726495</v>
       </c>
       <c r="J166">
         <v>8000</v>
@@ -9736,10 +9736,10 @@
         <v>1895005.380947487</v>
       </c>
       <c r="N166">
-        <v>1.667307692307692</v>
+        <v>1.722817230984068</v>
       </c>
       <c r="O166">
-        <v>1.799766355140187</v>
+        <v>1.865490279279885</v>
       </c>
       <c r="P166">
         <v>236.8756726184359</v>
@@ -9774,7 +9774,7 @@
         <v>198</v>
       </c>
       <c r="I167">
-        <v>10</v>
+        <v>21.19907407407406</v>
       </c>
       <c r="J167">
         <v>8000</v>
@@ -9789,10 +9789,10 @@
         <v>417788.7394214387</v>
       </c>
       <c r="N167">
-        <v>1.667307692307692</v>
+        <v>1.843792937469916</v>
       </c>
       <c r="O167">
-        <v>1.799766355140187</v>
+        <v>2.010158024452713</v>
       </c>
       <c r="P167">
         <v>52.22359242767983</v>
